--- a/SBU_Competitor_Mapping.xlsx
+++ b/SBU_Competitor_Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rpgnet-my.sharepoint.com/personal/sankuria_kecrpg_com/Documents/D Drive Backup/Apoorva/Competitor Dashboard/Online Migration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Competitor-Intelligence-Dashboard_Cron\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="628" documentId="13_ncr:1_{75BAAE1D-BD88-49CB-BA37-6676DC806970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B25DF69-0BCE-432C-AFFA-C3DD2365B536}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA51B79-C7CD-40FA-B92C-14F36115B0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E23101F4-9912-45FC-93F4-0A0DFC08459A}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="213">
   <si>
     <t>SBU</t>
   </si>
@@ -1172,6 +1172,18 @@
   <si>
     <t>"Bridge and Roof", "Bridge and Roof Company", "Bridge &amp; Roof", "Bridge and Roof Ltd", "Bridge and Roof Limited", "Bridge and Roof Engineering", "Bridge and Roof Contracting", "Bridge Roof Company"</t>
   </si>
+  <si>
+    <t>"Capacite Infraprojects", "Capacite Infraprojects Limited", "Capacite Infraprojects Ltd", "Capacite Infra", "Capacite Infrastructure", "Capacite", "CIL"</t>
+  </si>
+  <si>
+    <t>Megha Engineering and Infrastructures Limited</t>
+  </si>
+  <si>
+    <t>"Megha Engineering and Infrastructures", "Megha Engineering &amp; Infrastructures", "Megha Engineering and Infrastructures Limited", "Megha Engineering &amp; Infrastructures Limited", "Megha Engineering", "Megha Infrastructures", "Megha Infra", "Megha Group", "MEIL", "MEIL Group", "Megha Engineering Ltd", "Megha Engineering Limited"</t>
+  </si>
+  <si>
+    <t>Capacite InfraProjects Limited</t>
+  </si>
 </sst>
 </file>
 
@@ -1214,7 +1226,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1237,11 +1249,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1261,6 +1284,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1276,10 +1302,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1680,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}">
-  <dimension ref="B2:D83"/>
+  <dimension ref="B2:D85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="20.77734375" customWidth="1"/>
@@ -2588,6 +2610,28 @@
       </c>
       <c r="D83" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B84" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" s="9">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B85" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C85" s="9">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/SBU_Competitor_Mapping.xlsx
+++ b/SBU_Competitor_Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Competitor-Intelligence-Dashboard_Cron\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA51B79-C7CD-40FA-B92C-14F36115B0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A1A36A-71F7-43D0-B741-BA57ECBAAB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E23101F4-9912-45FC-93F4-0A0DFC08459A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Categories!$A$1:$A$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Competitor!$B$2:$D$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Competitor!$B$2:$D$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SBU!$B$2:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
   <si>
     <t>SBU</t>
   </si>
@@ -1184,12 +1184,114 @@
   <si>
     <t>Capacite InfraProjects Limited</t>
   </si>
+  <si>
+    <t>Adani Green Energy Limited</t>
+  </si>
+  <si>
+    <t>Reliance New Energy Limited</t>
+  </si>
+  <si>
+    <t>BluPine Energy Private Limited</t>
+  </si>
+  <si>
+    <t>Aditya Birla Renewables Limited</t>
+  </si>
+  <si>
+    <t>SAEL Industries Limited</t>
+  </si>
+  <si>
+    <t>ACME Solar Holdings Limited</t>
+  </si>
+  <si>
+    <t>Waaree Energies Limited</t>
+  </si>
+  <si>
+    <t>Suzlon Energy Limited</t>
+  </si>
+  <si>
+    <t>Inox Wind Limited</t>
+  </si>
+  <si>
+    <t>Vikran Engineering Limited</t>
+  </si>
+  <si>
+    <t>InSolare Energy Private Limited</t>
+  </si>
+  <si>
+    <t>Shivalaya Construction Co. Private Limited</t>
+  </si>
+  <si>
+    <t>"Adani Green Energy Limited", "Adani Green", "Adani Green Energy", "AGEL"</t>
+  </si>
+  <si>
+    <t>JSW Energy Limited</t>
+  </si>
+  <si>
+    <t>"JSW Energy Limited", "JSW Energy", "JSW Neo Energy", "JSW Neo Energy Limited"</t>
+  </si>
+  <si>
+    <t>"Reliance New Energy Limited", "Reliance New Energy", "RNEL", "Reliance New Energy Ltd"</t>
+  </si>
+  <si>
+    <t>"BluPine Energy Private Limited", "BluPine Energy", "BluPine"</t>
+  </si>
+  <si>
+    <t>ArcelorMittal Nippon Steel India</t>
+  </si>
+  <si>
+    <t>"ArcelorMittal Nippon Steel India", "ArcelorMittal", "AM/NS India", "AMNS India"</t>
+  </si>
+  <si>
+    <t>Greenko Group</t>
+  </si>
+  <si>
+    <t>"Greenko Group", "Greenko", "Greenko Energy Holdings"</t>
+  </si>
+  <si>
+    <t>"Aditya Birla Renewables Limited", "Aditya Birla Renewables", "ABREL"</t>
+  </si>
+  <si>
+    <t>Avaada Energy Private Limited</t>
+  </si>
+  <si>
+    <t>"Avaada Energy Private Limited", "Avaada", "Avaada Group", "Avaada Energy"</t>
+  </si>
+  <si>
+    <t>"SAEL Industries Limited", "SAEL", "SAEL Industries"</t>
+  </si>
+  <si>
+    <t>"ACME Solar Holdings Limited", "ACME Solar", "ACME Solar Holdings", "ACME Cleantech"</t>
+  </si>
+  <si>
+    <t>"Waaree Energies Limited", "Waaree", "Waaree Energies"</t>
+  </si>
+  <si>
+    <t>"Suzlon Energy Limited", "Suzlon", "Suzlon Energy"</t>
+  </si>
+  <si>
+    <t>"Inox Wind Limited", "Inox Wind"</t>
+  </si>
+  <si>
+    <t>"Vikran Engineering Limited", "Vikran Engineering", "Vikran"</t>
+  </si>
+  <si>
+    <t>"InSolare Energy Private Limited", "InSolare", "InSolare Energy"</t>
+  </si>
+  <si>
+    <t>"Shivalaya Construction Co. Private Limited", "Shivalaya Construction", "Shivalaya"</t>
+  </si>
+  <si>
+    <t>Fluence Energy India Private Limited</t>
+  </si>
+  <si>
+    <t>"Fluence Energy India Private Limited", "Fluence Energy", "Fluence", "Fluence Energy India"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1216,6 +1318,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1250,14 +1358,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1281,10 +1393,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1702,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}">
-  <dimension ref="B2:D85"/>
+  <dimension ref="B2:D152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="20.77734375" customWidth="1"/>
@@ -1770,7 +1882,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>75</v>
@@ -1814,7 +1926,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>78</v>
@@ -1847,7 +1959,7 @@
         <v>35</v>
       </c>
       <c r="C14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>81</v>
@@ -1990,7 +2102,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>93</v>
@@ -2034,7 +2146,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>97</v>
@@ -2085,7 +2197,7 @@
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C36" s="3">
@@ -2168,7 +2280,7 @@
       <c r="C43" s="3">
         <v>2</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2179,7 +2291,7 @@
       <c r="C44" s="3">
         <v>2</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="5" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2190,7 +2302,7 @@
       <c r="C45" s="3">
         <v>2</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="5" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2201,7 +2313,7 @@
       <c r="C46" s="3">
         <v>2</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2212,7 +2324,7 @@
       <c r="C47" s="3">
         <v>3</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2223,7 +2335,7 @@
       <c r="C48" s="3">
         <v>3</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2234,7 +2346,7 @@
       <c r="C49" s="3">
         <v>3</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2245,7 +2357,7 @@
       <c r="C50" s="3">
         <v>3</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2256,7 +2368,7 @@
       <c r="C51" s="3">
         <v>3</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2267,7 +2379,7 @@
       <c r="C52" s="3">
         <v>3</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2278,7 +2390,7 @@
       <c r="C53" s="3">
         <v>3</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2289,7 +2401,7 @@
       <c r="C54" s="3">
         <v>3</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>204</v>
       </c>
     </row>
@@ -2300,7 +2412,7 @@
       <c r="C55" s="3">
         <v>3</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2311,7 +2423,7 @@
       <c r="C56" s="3">
         <v>3</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2322,7 +2434,7 @@
       <c r="C57" s="3">
         <v>2</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2333,7 +2445,7 @@
       <c r="C58" s="3">
         <v>3</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2342,9 +2454,9 @@
         <v>187</v>
       </c>
       <c r="C59" s="3">
-        <v>2</v>
-      </c>
-      <c r="D59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2355,7 +2467,7 @@
       <c r="C60" s="3">
         <v>2</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2366,7 +2478,7 @@
       <c r="C61" s="3">
         <v>3</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2375,9 +2487,9 @@
         <v>189</v>
       </c>
       <c r="C62" s="3">
-        <v>3</v>
-      </c>
-      <c r="D62" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2388,7 +2500,7 @@
       <c r="C63" s="3">
         <v>3</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2397,9 +2509,9 @@
         <v>127</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
-      </c>
-      <c r="D64" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2410,7 +2522,7 @@
       <c r="C65" s="3">
         <v>3</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2421,7 +2533,7 @@
       <c r="C66" s="3">
         <v>2</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2432,7 +2544,7 @@
       <c r="C67" s="3">
         <v>3</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2443,7 +2555,7 @@
       <c r="C68" s="3">
         <v>3</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2454,7 +2566,7 @@
       <c r="C69" s="3">
         <v>3</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2465,7 +2577,7 @@
       <c r="C70" s="3">
         <v>2</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2476,7 +2588,7 @@
       <c r="C71" s="3">
         <v>1</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2487,7 +2599,7 @@
       <c r="C72" s="3">
         <v>1</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2498,7 +2610,7 @@
       <c r="C73" s="3">
         <v>2</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2509,7 +2621,7 @@
       <c r="C74" s="3">
         <v>3</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2520,7 +2632,7 @@
       <c r="C75" s="3">
         <v>3</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2531,7 +2643,7 @@
       <c r="C76" s="3">
         <v>3</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2542,7 +2654,7 @@
       <c r="C77" s="3">
         <v>3</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2553,7 +2665,7 @@
       <c r="C78" s="3">
         <v>2</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2564,7 +2676,7 @@
       <c r="C79" s="3">
         <v>2</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="1" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2575,7 +2687,7 @@
       <c r="C80" s="3">
         <v>3</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2586,7 +2698,7 @@
       <c r="C81" s="3">
         <v>2</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2597,7 +2709,7 @@
       <c r="C82" s="3">
         <v>3</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2608,37 +2720,415 @@
       <c r="C83" s="3">
         <v>2</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="84" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C84" s="9">
-        <v>1</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="85" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C85" s="9">
-        <v>1</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C85" s="3">
+        <v>1</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>211</v>
       </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B86" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C87" s="1">
+        <v>1</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B88" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="1">
+        <v>1</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B89" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" s="1">
+        <v>2</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B90" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B91" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="1">
+        <v>1</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B92" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C92" s="1">
+        <v>1</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B93" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B94" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B95" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C96" s="1">
+        <v>2</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B97" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B98" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" s="1">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B102" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C102" s="1">
+        <v>2</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C103" s="9"/>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C104" s="9"/>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C105" s="9"/>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C106" s="9"/>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C107" s="9"/>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C108" s="9"/>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+    </row>
+    <row r="124" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="125" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+    </row>
+    <row r="126" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
+    </row>
+    <row r="127" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+    </row>
+    <row r="128" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+    </row>
+    <row r="129" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
+    </row>
+    <row r="130" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+    </row>
+    <row r="131" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+    </row>
+    <row r="132" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+    </row>
+    <row r="133" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+    </row>
+    <row r="134" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+    </row>
+    <row r="135" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+    </row>
+    <row r="136" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+    </row>
+    <row r="137" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+    </row>
+    <row r="138" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+    </row>
+    <row r="139" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+    </row>
+    <row r="140" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+    </row>
+    <row r="141" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+    </row>
+    <row r="142" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
+    </row>
+    <row r="143" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+    </row>
+    <row r="144" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+    </row>
+    <row r="145" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+    </row>
+    <row r="146" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+    </row>
+    <row r="147" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+    </row>
+    <row r="148" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+    </row>
+    <row r="149" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+    </row>
+    <row r="150" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+    </row>
+    <row r="151" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+    </row>
+    <row r="152" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="B10 D10" name="Range1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-4221133713-561835035-3711840776-20806)"/>
   </protectedRanges>
-  <autoFilter ref="B2:D83" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}"/>
+  <autoFilter ref="B2:D85" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/SBU_Competitor_Mapping.xlsx
+++ b/SBU_Competitor_Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Competitor-Intelligence-Dashboard_Cron\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A1A36A-71F7-43D0-B741-BA57ECBAAB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27315DCF-A0D4-4223-B985-226A20236DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E23101F4-9912-45FC-93F4-0A0DFC08459A}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Categories!$A$1:$A$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Competitor!$B$2:$D$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Competitor!$B$2:$D$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SBU!$B$2:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="229">
   <si>
     <t>SBU</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Sterlite Power Transmission Limited</t>
   </si>
   <si>
-    <t>Hitachi Energy India Limited</t>
-  </si>
-  <si>
     <t>Techno Electric &amp; Engineering Company Limited</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>Skipper Limited</t>
   </si>
   <si>
-    <t>Hyosung T&amp;D India Private Limited</t>
-  </si>
-  <si>
     <t>Bajaj Electricals Limited</t>
   </si>
   <si>
@@ -113,15 +107,6 @@
   </si>
   <si>
     <t>Kernex Microsystems Private Limited</t>
-  </si>
-  <si>
-    <t>Siemens Energy</t>
-  </si>
-  <si>
-    <t>Hitachi Energy</t>
-  </si>
-  <si>
-    <t>Hyundai Engineering &amp; Construction Co.</t>
   </si>
   <si>
     <t>Saudi Services For Electro Mechanic Works Company Limited</t>
@@ -753,18 +738,6 @@
     <t>"Hindustan Construction Company", "Hindustan Construction Company Limited", "Hindustan Construction Company Ltd", "Hindustan Construction", "HCC", "HCCL"</t>
   </si>
   <si>
-    <t>"Hitachi Energy", "Hitachi Energy Ltd", "Hitachi Energy Limited", "Hitachi ABB Power Grids", "ABB Power Grids"</t>
-  </si>
-  <si>
-    <t>"Hitachi Energy India", "Hitachi Energy India Limited", "Hitachi Energy India Ltd", "Hitachi ABB Power Grids India", "ABB Power Grids India"</t>
-  </si>
-  <si>
-    <t>"Hyundai Engineering &amp; Construction", "Hyundai Engineering and Construction", "Hyundai Engineering &amp; Construction Co.", "Hyundai Engineering and Construction Co.", "Hyundai E&amp;C", "HEC", "Hyundai Construction"</t>
-  </si>
-  <si>
-    <t>"Hyosung T&amp;D India", "Hyosung TandD India", "Hyosung Transmission &amp; Distribution India", "Hyosung T&amp;D", "Hyosung India", "HTIPL"</t>
-  </si>
-  <si>
     <t>"Jackson Electricals &amp; Infrastructure", "Jackson Electricals and Infrastructure", "Jackson Electricals", "Jackson Infrastructure", "JEIPL"</t>
   </si>
   <si>
@@ -799,9 +772,6 @@
   </si>
   <si>
     <t>"Shapoorji Pallonji &amp; Company", "Shapoorji Pallonji and Company", "Shapoorji Pallonji &amp; Co", "Shapoorji Pallonji", "Shapoorji Pallonji Group", "SP Group", "SPCPL"</t>
-  </si>
-  <si>
-    <t>"Siemens Energy", "Siemens Energy AG", "Siemens Energy Ltd", "Siemens Energy Limited"</t>
   </si>
   <si>
     <t>"Simplex Infrastructures", "Simplex Infrastructures Limited", "Simplex Infrastructures Ltd", "Simplex", "SIL"</t>
@@ -939,18 +909,6 @@
     <t>Algihaz Holdings</t>
   </si>
   <si>
-    <t>"CMEC", "China Machinery Engineering Corporation", "China Machinery Engineering", "CMEC International", "CMEC Power", "CMEC T&amp;D", "CMEC Transmission", "China Machinery Engineering Corp"</t>
-  </si>
-  <si>
-    <t>CMEC (China)</t>
-  </si>
-  <si>
-    <t>"Sinohydro", "Sinohydro Corporation", "Sinohydro Group", "Sinohydro Limited", "Sinohydro Power", "PowerChina Sinohydro", "Power Construction Corporation of China"</t>
-  </si>
-  <si>
-    <t>Sinohydro Corporation Limited</t>
-  </si>
-  <si>
     <t>"JSIW", "JSIW Group", "JSIW International", "JSIW Engineering", "JSIW Contracting", "JSIW Construction", "JSIW Power", "JSIW T&amp;D", "JSIW Transmission"</t>
   </si>
   <si>
@@ -1008,12 +966,6 @@
     <t>"KP Energy", "K P Energy", "KP Energy Ltd", "KP Energy Limited", "KP Energy Group", "KP Energy Engineering", "KP Energy Solar", "KP Energy Wind", "KP Energy Power", "KP Energy Renewable"</t>
   </si>
   <si>
-    <t>"China Southern Power Grid", "CSG", "China Southern Grid", "Southern Power Grid China", "CSG Corporation", "China Southern Power Grid Company", "CSPG", "Southern Grid Corporation", "China Southern Power", "Guangdong Power Grid"</t>
-  </si>
-  <si>
-    <t>"State Grid", "State Grid China", "State Grid Corporation", "State Grid Corporation of China", "SGCC", "State Grid Corp", "China State Grid", "State Grid International", "State Grid Power"</t>
-  </si>
-  <si>
     <t>"PLP", "Preformed Line Products", "PLP Group", "PLP International", "PLP Power", "PLP T&amp;D", "Preformed Line Products Company", "PLP Ltd", "PLP Limited"</t>
   </si>
   <si>
@@ -1063,12 +1015,6 @@
   </si>
   <si>
     <t>Power Mech Projects Limited</t>
-  </si>
-  <si>
-    <t>China Southern Power Grid Company Limited</t>
-  </si>
-  <si>
-    <t>State Grid Corporation of China</t>
   </si>
   <si>
     <t>Preformed Line Products Company (PLP)</t>
@@ -1396,7 +1342,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1752,7 +1698,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
@@ -1760,7 +1706,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
@@ -1768,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
@@ -1776,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
@@ -1784,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
@@ -1792,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
@@ -1800,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
@@ -1814,7 +1760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}">
-  <dimension ref="B2:D152"/>
+  <dimension ref="B2:D143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="20.77734375" customWidth="1"/>
@@ -1827,1143 +1773,1080 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3">
         <v>2</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3">
         <v>2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3">
         <v>3</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C19" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3">
         <v>2</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C21" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
         <v>2</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="3">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="3">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="3">
         <v>2</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="3">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="3">
-        <v>1</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C37" s="3">
         <v>1</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>104</v>
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="C39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>105</v>
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="C41" s="3">
-        <v>2</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>107</v>
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="C42" s="3">
-        <v>1</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>108</v>
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="C43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="C44" s="3">
-        <v>2</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="C45" s="3">
-        <v>2</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>131</v>
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C47" s="3">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C48" s="3">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C49" s="3">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="C50" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C51" s="3">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="C52" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="C53" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>208</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C54" s="3">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B55" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C55" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B56" s="3" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C56" s="3">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="C57" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C58" s="3">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B59" s="3" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C61" s="3">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C62" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C63" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C64" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C65" s="3">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C66" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C67" s="3">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C68" s="3">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="41.4" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C69" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C70" s="3">
         <v>2</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C71" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B73" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C73" s="3">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B74" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="3">
         <v>2</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B74" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C74" s="3">
-        <v>3</v>
-      </c>
       <c r="D74" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C75" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B77" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C77" s="1">
+        <v>1</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B78" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B79" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79" s="1">
+        <v>1</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B81" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B82" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C82" s="1">
+        <v>1</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C83" s="1">
+        <v>1</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="1">
+        <v>1</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B85" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C76" s="3">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C77" s="3">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B78" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C78" s="3">
-        <v>2</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B79" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C79" s="3">
-        <v>2</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B80" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C80" s="3">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B81" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C81" s="3">
-        <v>2</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B82" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C82" s="3">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="3">
-        <v>2</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C84" s="3">
-        <v>1</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B85" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C85" s="3">
+      <c r="C85" s="1">
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="C87" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B94" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C94" s="1">
-        <v>1</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="C94" s="9"/>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B95" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C95" s="1">
-        <v>1</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>238</v>
-      </c>
+      <c r="C95" s="9"/>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B96" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C96" s="1">
-        <v>2</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B97" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C97" s="1">
-        <v>1</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B98" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B99" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C99" s="1">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B101" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C101" s="1">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B102" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C102" s="1">
-        <v>2</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C96" s="9"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="9"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="9"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="9"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B103" s="9"/>
       <c r="C103" s="9"/>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B104" s="9"/>
       <c r="C104" s="9"/>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B105" s="9"/>
       <c r="C105" s="9"/>
     </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B106" s="9"/>
       <c r="C106" s="9"/>
     </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B107" s="9"/>
       <c r="C107" s="9"/>
     </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B108" s="9"/>
       <c r="C108" s="9"/>
     </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
     </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
     </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
     </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
     </row>
@@ -2975,43 +2858,43 @@
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-    </row>
-    <row r="124" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="115" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="116" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+    </row>
+    <row r="117" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+    </row>
+    <row r="118" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+    </row>
+    <row r="119" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+    </row>
+    <row r="120" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+    </row>
+    <row r="121" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+    </row>
+    <row r="122" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+    </row>
+    <row r="123" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+    </row>
+    <row r="124" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+    </row>
     <row r="125" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -3087,48 +2970,12 @@
     <row r="143" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
-    </row>
-    <row r="144" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-    </row>
-    <row r="145" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-    </row>
-    <row r="146" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-    </row>
-    <row r="147" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
-    </row>
-    <row r="148" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B148" s="8"/>
-      <c r="C148" s="8"/>
-    </row>
-    <row r="149" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
-    </row>
-    <row r="150" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-    </row>
-    <row r="151" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
-    </row>
-    <row r="152" spans="2:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="8"/>
-      <c r="C152" s="8"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="B10 D10" name="Range1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-4221133713-561835035-3711840776-20806)"/>
   </protectedRanges>
-  <autoFilter ref="B2:D85" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}"/>
+  <autoFilter ref="B2:D93" xr:uid="{736360B8-597D-4267-8E49-40BA5E740079}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3143,62 +2990,62 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3216,77 +3063,77 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
